--- a/demo 4 (alpha interpolated)/Pb210_results/CFCS modeling data/SAR_model_summaries.xlsx
+++ b/demo 4 (alpha interpolated)/Pb210_results/CFCS modeling data/SAR_model_summaries.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.542237427249186</v>
+        <v>2.541757912387572</v>
       </c>
       <c r="D2">
-        <v>0.04794126926571813</v>
+        <v>0.04804697012733745</v>
       </c>
       <c r="E2">
-        <v>53.02816271214352</v>
+        <v>52.90152335623301</v>
       </c>
       <c r="F2">
-        <v>4.984871412481907E-28</v>
+        <v>5.301677796828538E-28</v>
       </c>
       <c r="G2">
-        <v>0.946962520218093</v>
+        <v>0.9470196289264795</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.06519108262162894</v>
+        <v>-0.0653719134693901</v>
       </c>
       <c r="D3">
-        <v>0.002966069878096848</v>
+        <v>0.002972609465941306</v>
       </c>
       <c r="E3">
-        <v>-21.97894361931156</v>
+        <v>-21.99142343398595</v>
       </c>
       <c r="F3">
-        <v>2.554659410286256E-18</v>
+        <v>2.519062122148504E-18</v>
       </c>
       <c r="G3">
-        <v>0.946962520218093</v>
+        <v>0.9470196289264795</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>6.125650276708487</v>
+        <v>6.193291016509459</v>
       </c>
       <c r="D4">
-        <v>0.3738810867253288</v>
+        <v>0.3789112252380045</v>
       </c>
       <c r="E4">
-        <v>16.38395333222268</v>
+        <v>16.34496579672266</v>
       </c>
       <c r="F4">
-        <v>3.292937934340875E-06</v>
+        <v>3.339431624619589E-06</v>
       </c>
       <c r="G4">
-        <v>0.9740168706873465</v>
+        <v>0.9740172634126486</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.1952096251853498</v>
+        <v>-0.1978374745758323</v>
       </c>
       <c r="D5">
-        <v>0.01202787048136943</v>
+        <v>0.01218969159691106</v>
       </c>
       <c r="E5">
-        <v>-16.2297744632119</v>
+        <v>-16.22989991198509</v>
       </c>
       <c r="F5">
-        <v>3.481327497516628E-06</v>
+        <v>3.481169195332913E-06</v>
       </c>
       <c r="G5">
-        <v>0.9740168706873465</v>
+        <v>0.9740172634126486</v>
       </c>
     </row>
   </sheetData>
